--- a/templates/_masters/LGL-002-tot-filing-calendar-DEMO.xlsx
+++ b/templates/_masters/LGL-002-tot-filing-calendar-DEMO.xlsx
@@ -564,7 +564,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="3">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -590,19 +590,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00E2C884"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <b val="1"/>
-        <color rgb="00B91C1C"/>
-        <sz val="11"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F8B4B4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4505,7 +4492,7 @@
     <cfRule type="expression" priority="2" dxfId="2">
       <formula>AND($C6-TODAY()&gt;=7,$C6-TODAY()&lt;=30,$E6&lt;&gt;"Filed",$E6&lt;&gt;"Paid",$E6&lt;&gt;"N/A")</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="3">
+    <cfRule type="expression" priority="3" dxfId="1">
       <formula>AND($C6&lt;TODAY(),$E6&lt;&gt;"Filed",$E6&lt;&gt;"Paid",$E6&lt;&gt;"N/A")</formula>
     </cfRule>
   </conditionalFormatting>
